--- a/samples/test-pack/Bookings.xlsx
+++ b/samples/test-pack/Bookings.xlsx
@@ -880,7 +880,7 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>51</v>
@@ -1088,7 +1088,7 @@
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1378,7 +1378,7 @@
         <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
